--- a/output/yearly_benthic_cover_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_82_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.91827580667935</v>
+        <v>45.38444046511779</v>
       </c>
       <c r="M2" t="n">
-        <v>98.92628159154117</v>
+        <v>99.93718860118085</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.94529820536889</v>
+        <v>87.94332489248336</v>
       </c>
       <c r="C3" t="n">
-        <v>45.82530763086157</v>
+        <v>45.87632783186665</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228598528084325</v>
+        <v>2.228554731284039</v>
       </c>
       <c r="E3" t="n">
-        <v>5.643077327200485</v>
+        <v>5.671904540084166</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428661760281082</v>
+        <v>0.7428515770946799</v>
       </c>
       <c r="G3" t="n">
-        <v>33.93804677499936</v>
+        <v>33.95581725305549</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17184409729298</v>
+        <v>34.17117254635527</v>
       </c>
       <c r="I3" t="n">
-        <v>6.577951701587959</v>
+        <v>6.530201887767969</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642913600175676</v>
+        <v>4.642822356841749</v>
       </c>
       <c r="K3" t="n">
-        <v>12.05470179463111</v>
+        <v>12.05667510751665</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8838618462974</v>
+        <v>48.83257780059681</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7638712717901</v>
+        <v>106.7655807399801</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.10153337311796</v>
+        <v>87.02591149258051</v>
       </c>
       <c r="C4" t="n">
-        <v>42.62242837705966</v>
+        <v>42.58868718602776</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188213447060347</v>
+        <v>2.18426168470923</v>
       </c>
       <c r="E4" t="n">
-        <v>6.456342468210861</v>
+        <v>6.468041013038293</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444278306108059</v>
+        <v>0.7444031913214259</v>
       </c>
       <c r="G4" t="n">
-        <v>33.32304557512777</v>
+        <v>33.28093744240407</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24368020809707</v>
+        <v>34.24254680078558</v>
       </c>
       <c r="I4" t="n">
-        <v>5.493149902693577</v>
+        <v>5.453201414563</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652673941317536</v>
+        <v>4.652519945758911</v>
       </c>
       <c r="K4" t="n">
-        <v>12.89846662688205</v>
+        <v>12.97408850741948</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29638411545861</v>
+        <v>44.25582980967032</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81727911940033</v>
+        <v>99.81860550311757</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.03143294576273</v>
+        <v>85.82328467938527</v>
       </c>
       <c r="C5" t="n">
-        <v>42.40486638013977</v>
+        <v>42.23240560363374</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136206661297423</v>
+        <v>2.12536929382923</v>
       </c>
       <c r="E5" t="n">
-        <v>7.06718905828293</v>
+        <v>7.052376960151654</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457505123375803</v>
+        <v>0.7457193835971814</v>
       </c>
       <c r="G5" t="n">
-        <v>32.53106410982695</v>
+        <v>32.38361181954868</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30452356752869</v>
+        <v>34.30309164547034</v>
       </c>
       <c r="I5" t="n">
-        <v>4.585758334379275</v>
+        <v>4.552369429305795</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660940702109876</v>
+        <v>4.660746147482383</v>
       </c>
       <c r="K5" t="n">
-        <v>13.96856705423728</v>
+        <v>14.17671532061473</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47397906832592</v>
+        <v>43.43940125868033</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84741250270297</v>
+        <v>99.8485221829288</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.76298236443247</v>
+        <v>84.44858440770392</v>
       </c>
       <c r="C6" t="n">
-        <v>41.84867064018954</v>
+        <v>41.56465071729342</v>
       </c>
       <c r="D6" t="n">
-        <v>2.074397570726037</v>
+        <v>2.058151630629706</v>
       </c>
       <c r="E6" t="n">
-        <v>7.500576194912196</v>
+        <v>7.462557779680821</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468729161814657</v>
+        <v>0.7468377107317179</v>
       </c>
       <c r="G6" t="n">
-        <v>31.58980897549147</v>
+        <v>31.35943652973409</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35615414434742</v>
+        <v>34.35453469365902</v>
       </c>
       <c r="I6" t="n">
-        <v>3.827216836639729</v>
+        <v>3.799330371195329</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66795572613416</v>
+        <v>4.667735692073236</v>
       </c>
       <c r="K6" t="n">
-        <v>15.23701763556752</v>
+        <v>15.55141559229608</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78692954828797</v>
+        <v>42.75747898404089</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87261782404502</v>
+        <v>99.87354529363039</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.23684007733979</v>
+        <v>82.75937206550128</v>
       </c>
       <c r="C7" t="n">
-        <v>40.9170712641962</v>
+        <v>40.46545608235083</v>
       </c>
       <c r="D7" t="n">
-        <v>2.000045893279001</v>
+        <v>1.975625924965217</v>
       </c>
       <c r="E7" t="n">
-        <v>7.763974171723029</v>
+        <v>7.691690152032518</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478280555305471</v>
+        <v>0.7477913141256987</v>
       </c>
       <c r="G7" t="n">
-        <v>30.4575499906638</v>
+        <v>30.10201720729804</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40009055440517</v>
+        <v>34.39840044978214</v>
       </c>
       <c r="I7" t="n">
-        <v>3.19342606467232</v>
+        <v>3.170151304012048</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673925347065919</v>
+        <v>4.673695713285617</v>
       </c>
       <c r="K7" t="n">
-        <v>16.76315992266023</v>
+        <v>17.24062793449872</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21345723434802</v>
+        <v>42.18837902839503</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89368842120444</v>
+        <v>99.89446304524458</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.91749736090975</v>
+        <v>87.63277257732977</v>
       </c>
       <c r="C8" t="n">
-        <v>43.18765363959111</v>
+        <v>42.73386578641905</v>
       </c>
       <c r="D8" t="n">
-        <v>2.004205011955531</v>
+        <v>1.979872510569928</v>
       </c>
       <c r="E8" t="n">
-        <v>9.566740819602787</v>
+        <v>9.503170142807903</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493831726621303</v>
+        <v>0.7493986831067219</v>
       </c>
       <c r="G8" t="n">
-        <v>30.95713386297468</v>
+        <v>30.59328041162698</v>
       </c>
       <c r="H8" t="n">
-        <v>34.471625942458</v>
+        <v>34.47233942290921</v>
       </c>
       <c r="I8" t="n">
-        <v>5.484763722118297</v>
+        <v>5.65096963689202</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683644829138314</v>
+        <v>4.683741769417012</v>
       </c>
       <c r="K8" t="n">
-        <v>12.08250263909028</v>
+        <v>12.36722742267023</v>
       </c>
       <c r="L8" t="n">
-        <v>44.54739766261386</v>
+        <v>44.71094515775449</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81755394129524</v>
+        <v>99.81203836684377</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.80802499158823</v>
+        <v>85.56437843426856</v>
       </c>
       <c r="C9" t="n">
-        <v>41.92976323705672</v>
+        <v>41.5421844990631</v>
       </c>
       <c r="D9" t="n">
-        <v>1.908180719532913</v>
+        <v>1.886005598428249</v>
       </c>
       <c r="E9" t="n">
-        <v>9.87151245071076</v>
+        <v>9.838918688326181</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507160900724527</v>
+        <v>0.7507760126454081</v>
       </c>
       <c r="G9" t="n">
-        <v>29.47393386252963</v>
+        <v>29.14283511820893</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53294014333282</v>
+        <v>34.53569658168878</v>
       </c>
       <c r="I9" t="n">
-        <v>4.578766162456821</v>
+        <v>4.717796355937228</v>
       </c>
       <c r="J9" t="n">
-        <v>4.691975562952829</v>
+        <v>4.692350079033801</v>
       </c>
       <c r="K9" t="n">
-        <v>14.19197500841178</v>
+        <v>14.43562156573144</v>
       </c>
       <c r="L9" t="n">
-        <v>43.72590720669489</v>
+        <v>43.86522255640291</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84764545216339</v>
+        <v>99.84302862119743</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.3607255574403</v>
+        <v>83.19841696846113</v>
       </c>
       <c r="C10" t="n">
-        <v>40.1929834334835</v>
+        <v>39.90782344568151</v>
       </c>
       <c r="D10" t="n">
-        <v>1.797724112721896</v>
+        <v>1.779622049030067</v>
       </c>
       <c r="E10" t="n">
-        <v>9.937003366887533</v>
+        <v>9.94021996143414</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7518632483272726</v>
+        <v>0.7519604623749645</v>
       </c>
       <c r="G10" t="n">
-        <v>27.76781101446717</v>
+        <v>27.49898091014889</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58570942305454</v>
+        <v>34.59018126924837</v>
       </c>
       <c r="I10" t="n">
-        <v>3.821469089936445</v>
+        <v>3.937699426381172</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699145302045453</v>
+        <v>4.699752889843529</v>
       </c>
       <c r="K10" t="n">
-        <v>16.6392744425597</v>
+        <v>16.80158303153887</v>
       </c>
       <c r="L10" t="n">
-        <v>43.04055417499967</v>
+        <v>43.1595436240036</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87281205104287</v>
+        <v>99.86895010122397</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.84660156329325</v>
+        <v>80.82467880350424</v>
       </c>
       <c r="C11" t="n">
-        <v>38.27103734408134</v>
+        <v>38.14394791613968</v>
       </c>
       <c r="D11" t="n">
-        <v>1.685521744270094</v>
+        <v>1.674175238287498</v>
       </c>
       <c r="E11" t="n">
-        <v>9.848256975680384</v>
+        <v>9.898882272959549</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752851745754662</v>
+        <v>0.7529794741722058</v>
       </c>
       <c r="G11" t="n">
-        <v>26.03472297248282</v>
+        <v>25.86960132518232</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63118030471445</v>
+        <v>34.63705581192147</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1887444094242</v>
+        <v>3.28586296740492</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705323410966637</v>
+        <v>4.706121713576287</v>
       </c>
       <c r="K11" t="n">
-        <v>19.15339843670675</v>
+        <v>19.17532119649575</v>
       </c>
       <c r="L11" t="n">
-        <v>42.46941230004703</v>
+        <v>42.57135034774288</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89384808083511</v>
+        <v>99.8906194603783</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.23496218715063</v>
+        <v>78.39606445573976</v>
       </c>
       <c r="C12" t="n">
-        <v>36.15259523002091</v>
+        <v>36.22339381942108</v>
       </c>
       <c r="D12" t="n">
-        <v>1.570127455222476</v>
+        <v>1.567409382418387</v>
       </c>
       <c r="E12" t="n">
-        <v>9.617408184388648</v>
+        <v>9.724510480398788</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537050772463331</v>
+        <v>0.7538571653901066</v>
       </c>
       <c r="G12" t="n">
-        <v>24.25233223313207</v>
+        <v>24.21983966146245</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67043355333132</v>
+        <v>34.67742960794491</v>
       </c>
       <c r="I12" t="n">
-        <v>2.660298951040185</v>
+        <v>2.741410874436945</v>
       </c>
       <c r="J12" t="n">
-        <v>4.710656732789581</v>
+        <v>4.711607283688168</v>
       </c>
       <c r="K12" t="n">
-        <v>21.76503781284938</v>
+        <v>21.60393554426026</v>
       </c>
       <c r="L12" t="n">
-        <v>41.99379072353458</v>
+        <v>42.08139666500185</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91142376640488</v>
+        <v>99.90872602868319</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.58160535798166</v>
+        <v>75.98899891459052</v>
       </c>
       <c r="C13" t="n">
-        <v>33.9097020862428</v>
+        <v>34.23930265885895</v>
       </c>
       <c r="D13" t="n">
-        <v>1.453994759049866</v>
+        <v>1.462632647924134</v>
       </c>
       <c r="E13" t="n">
-        <v>9.275915067974553</v>
+        <v>9.455588839696347</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7544427064364599</v>
+        <v>0.7546133806014915</v>
       </c>
       <c r="G13" t="n">
-        <v>22.4585359898147</v>
+        <v>22.60081419296167</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70436449607716</v>
+        <v>34.71221550766862</v>
       </c>
       <c r="I13" t="n">
-        <v>2.219085423401042</v>
+        <v>2.286800716978924</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715266915227875</v>
+        <v>4.716333628759323</v>
       </c>
       <c r="K13" t="n">
-        <v>24.41839464201835</v>
+        <v>24.0110010854095</v>
       </c>
       <c r="L13" t="n">
-        <v>41.59800607865439</v>
+        <v>41.67354595366386</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92610280691554</v>
+        <v>99.92384969793231</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.98921825860735</v>
+        <v>83.11770939813917</v>
       </c>
       <c r="C14" t="n">
-        <v>38.44195699789776</v>
+        <v>38.54895715957574</v>
       </c>
       <c r="D14" t="n">
-        <v>1.455766214846723</v>
+        <v>1.464488903496544</v>
       </c>
       <c r="E14" t="n">
-        <v>11.79226330235869</v>
+        <v>11.87167185763139</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553618719956169</v>
+        <v>0.7555710751358948</v>
       </c>
       <c r="G14" t="n">
-        <v>24.48540087212708</v>
+        <v>24.50614855543012</v>
       </c>
       <c r="H14" t="n">
-        <v>36.7461489259049</v>
+        <v>36.63292068536673</v>
       </c>
       <c r="I14" t="n">
-        <v>3.033265371401722</v>
+        <v>3.16458910147914</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721011699972606</v>
+        <v>4.722319219599344</v>
       </c>
       <c r="K14" t="n">
-        <v>17.01078174139266</v>
+        <v>16.88229060186083</v>
       </c>
       <c r="L14" t="n">
-        <v>44.44627544975894</v>
+        <v>44.46339964021468</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89901418904935</v>
+        <v>99.89464740165126</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.07766551521418</v>
+        <v>82.41733058592948</v>
       </c>
       <c r="C15" t="n">
-        <v>37.99852637507408</v>
+        <v>38.3370278435786</v>
       </c>
       <c r="D15" t="n">
-        <v>1.422058080210843</v>
+        <v>1.438919132601911</v>
       </c>
       <c r="E15" t="n">
-        <v>11.94093429177128</v>
+        <v>12.10438968935545</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561380905630845</v>
+        <v>0.756377817878404</v>
       </c>
       <c r="G15" t="n">
-        <v>23.91844363627857</v>
+        <v>24.07827463806816</v>
       </c>
       <c r="H15" t="n">
-        <v>36.78390969215044</v>
+        <v>36.67203460048653</v>
       </c>
       <c r="I15" t="n">
-        <v>2.530318658220692</v>
+        <v>2.639973345799027</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725863066019278</v>
+        <v>4.727361361740027</v>
       </c>
       <c r="K15" t="n">
-        <v>17.92233448478582</v>
+        <v>17.58266941407051</v>
       </c>
       <c r="L15" t="n">
-        <v>43.99488176871228</v>
+        <v>43.99239748953202</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91574262857218</v>
+        <v>99.91209474718114</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.51490149057128</v>
+        <v>79.92347543264766</v>
       </c>
       <c r="C16" t="n">
-        <v>35.82624322115595</v>
+        <v>36.25076908931639</v>
       </c>
       <c r="D16" t="n">
-        <v>1.325475999028165</v>
+        <v>1.344770102074664</v>
       </c>
       <c r="E16" t="n">
-        <v>11.48168456119603</v>
+        <v>11.67939453095763</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568070647639883</v>
+        <v>0.7570724584219759</v>
       </c>
       <c r="G16" t="n">
-        <v>22.29397196582482</v>
+        <v>22.50282389689709</v>
       </c>
       <c r="H16" t="n">
-        <v>36.81645333318577</v>
+        <v>36.70571338038547</v>
       </c>
       <c r="I16" t="n">
-        <v>2.110464411797577</v>
+        <v>2.201998198773486</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730044154774927</v>
+        <v>4.73170286513735</v>
       </c>
       <c r="K16" t="n">
-        <v>20.48509850942873</v>
+        <v>20.07652456735234</v>
       </c>
       <c r="L16" t="n">
-        <v>43.61837164002029</v>
+        <v>43.5993737503924</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92971337060497</v>
+        <v>99.92666740706113</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.28795747939512</v>
+        <v>81.79357718203627</v>
       </c>
       <c r="C17" t="n">
-        <v>37.10217546034294</v>
+        <v>37.58833366839492</v>
       </c>
       <c r="D17" t="n">
-        <v>1.326631102453074</v>
+        <v>1.345991706354453</v>
       </c>
       <c r="E17" t="n">
-        <v>12.29144915204574</v>
+        <v>12.52848848502941</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574665941957885</v>
+        <v>0.7577601915548672</v>
       </c>
       <c r="G17" t="n">
-        <v>22.7589617885427</v>
+        <v>22.99023895036099</v>
       </c>
       <c r="H17" t="n">
-        <v>37.29409896255569</v>
+        <v>37.20603049833728</v>
       </c>
       <c r="I17" t="n">
-        <v>2.125183665878434</v>
+        <v>2.229066153181345</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734166213723679</v>
+        <v>4.736001197217921</v>
       </c>
       <c r="K17" t="n">
-        <v>18.71204252060491</v>
+        <v>18.20642281796372</v>
       </c>
       <c r="L17" t="n">
-        <v>44.11500424374246</v>
+        <v>44.13100874423447</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92922222469031</v>
+        <v>99.92576523059311</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.91116592236763</v>
+        <v>79.54369615073681</v>
       </c>
       <c r="C18" t="n">
-        <v>35.05288147824853</v>
+        <v>35.68219082327545</v>
       </c>
       <c r="D18" t="n">
-        <v>1.240880396865135</v>
+        <v>1.264829408695792</v>
       </c>
       <c r="E18" t="n">
-        <v>11.79234053604397</v>
+        <v>12.08286366059576</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580336737729227</v>
+        <v>0.7583505077132926</v>
       </c>
       <c r="G18" t="n">
-        <v>21.2878693136205</v>
+        <v>21.60394466034138</v>
       </c>
       <c r="H18" t="n">
-        <v>37.32201929862244</v>
+        <v>37.23501502568355</v>
       </c>
       <c r="I18" t="n">
-        <v>1.772312242361894</v>
+        <v>1.859002214498964</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737710461080768</v>
+        <v>4.73969067320808</v>
       </c>
       <c r="K18" t="n">
-        <v>21.08883407763235</v>
+        <v>20.45630384926318</v>
       </c>
       <c r="L18" t="n">
-        <v>43.79925156451139</v>
+        <v>43.79958682320633</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94096712039229</v>
+        <v>99.93808149574495</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.00105634809972</v>
+        <v>78.70684459015979</v>
       </c>
       <c r="C19" t="n">
-        <v>34.41242974804558</v>
+        <v>35.13133142878294</v>
       </c>
       <c r="D19" t="n">
-        <v>1.208624545097305</v>
+        <v>1.235355942829267</v>
       </c>
       <c r="E19" t="n">
-        <v>11.73255885435855</v>
+        <v>12.05966910825581</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758513273790417</v>
+        <v>0.7588483822523926</v>
       </c>
       <c r="G19" t="n">
-        <v>20.73450546101407</v>
+        <v>21.10052252202674</v>
       </c>
       <c r="H19" t="n">
-        <v>37.34563255186942</v>
+        <v>37.25946066889964</v>
       </c>
       <c r="I19" t="n">
-        <v>1.480513700779848</v>
+        <v>1.550185576818495</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740707961190107</v>
+        <v>4.742802389077455</v>
       </c>
       <c r="K19" t="n">
-        <v>21.99894365190027</v>
+        <v>21.2931554098402</v>
       </c>
       <c r="L19" t="n">
-        <v>43.53930734713958</v>
+        <v>43.5238742109741</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95068074708544</v>
+        <v>99.94836104959724</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.381694568307</v>
+        <v>76.29172560275856</v>
       </c>
       <c r="C20" t="n">
-        <v>32.02046725735369</v>
+        <v>32.95458052029888</v>
       </c>
       <c r="D20" t="n">
-        <v>1.115223757693591</v>
+        <v>1.149262815112768</v>
       </c>
       <c r="E20" t="n">
-        <v>11.03162252424908</v>
+        <v>11.43464446930208</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589273156193257</v>
+        <v>0.7592769346804622</v>
       </c>
       <c r="G20" t="n">
-        <v>19.13217234247775</v>
+        <v>19.6300070880594</v>
       </c>
       <c r="H20" t="n">
-        <v>37.36601802769143</v>
+        <v>37.2805025959982</v>
       </c>
       <c r="I20" t="n">
-        <v>1.23443487795502</v>
+        <v>1.29255085785276</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743295722620786</v>
+        <v>4.74548084175289</v>
       </c>
       <c r="K20" t="n">
-        <v>24.61830543169302</v>
+        <v>23.70827439724144</v>
       </c>
       <c r="L20" t="n">
-        <v>43.32010193037606</v>
+        <v>43.2940843719925</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95887461942277</v>
+        <v>99.95693928953281</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.54937725808192</v>
+        <v>82.22324888227693</v>
       </c>
       <c r="C21" t="n">
-        <v>35.83669255998726</v>
+        <v>36.56029418205877</v>
       </c>
       <c r="D21" t="n">
-        <v>1.116042003936131</v>
+        <v>1.150167601151538</v>
       </c>
       <c r="E21" t="n">
-        <v>13.09006652863466</v>
+        <v>13.40044093504431</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594841450628184</v>
+        <v>0.7598746945322777</v>
       </c>
       <c r="G21" t="n">
-        <v>20.89739347485467</v>
+        <v>21.27859396189555</v>
       </c>
       <c r="H21" t="n">
-        <v>39.14461744009159</v>
+        <v>38.94298526608126</v>
       </c>
       <c r="I21" t="n">
-        <v>1.794997758859445</v>
+        <v>1.941969582745277</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746775906642616</v>
+        <v>4.749216840826738</v>
       </c>
       <c r="K21" t="n">
-        <v>18.45062274191807</v>
+        <v>17.77675111772306</v>
       </c>
       <c r="L21" t="n">
-        <v>45.65289530729438</v>
+        <v>45.59827330284922</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94021060919971</v>
+        <v>99.93531860263104</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_82_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.38444046511779</v>
+        <v>45.35043813460899</v>
       </c>
       <c r="M2" t="n">
-        <v>99.93718860118085</v>
+        <v>100.5884629968408</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.94332489248336</v>
+        <v>88.00211194501367</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87632783186665</v>
+        <v>45.93593280295305</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228554731284039</v>
+        <v>2.228660463097383</v>
       </c>
       <c r="E3" t="n">
-        <v>5.671904540084166</v>
+        <v>5.709032593426138</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428515770946799</v>
+        <v>0.742886821032461</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95581725305549</v>
+        <v>33.97591898637718</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17117254635527</v>
+        <v>34.1727937674932</v>
       </c>
       <c r="I3" t="n">
-        <v>6.530201887767969</v>
+        <v>6.529776682134408</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642822356841749</v>
+        <v>4.643042631452881</v>
       </c>
       <c r="K3" t="n">
-        <v>12.05667510751665</v>
+        <v>11.99788805498635</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83257780059681</v>
+        <v>48.83178626651026</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7655807399801</v>
+        <v>106.7656071244497</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.02591149258051</v>
+        <v>87.03019665194029</v>
       </c>
       <c r="C4" t="n">
-        <v>42.58868718602776</v>
+        <v>42.59149699893401</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18426168470923</v>
+        <v>2.181527688555789</v>
       </c>
       <c r="E4" t="n">
-        <v>6.468041013038293</v>
+        <v>6.49710275461477</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444031913214259</v>
+        <v>0.7444383310710321</v>
       </c>
       <c r="G4" t="n">
-        <v>33.28093744240407</v>
+        <v>33.25738004518612</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24254680078558</v>
+        <v>34.24416322926747</v>
       </c>
       <c r="I4" t="n">
-        <v>5.453201414563</v>
+        <v>5.452845034051149</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652519945758911</v>
+        <v>4.65273956919395</v>
       </c>
       <c r="K4" t="n">
-        <v>12.97408850741948</v>
+        <v>12.96980334805973</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25582980967032</v>
+        <v>44.25731696739142</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81860550311757</v>
+        <v>99.81861731438515</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.82328467938527</v>
+        <v>85.81282373951268</v>
       </c>
       <c r="C5" t="n">
-        <v>42.23240560363374</v>
+        <v>42.22041549506277</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12536929382923</v>
+        <v>2.12194491050791</v>
       </c>
       <c r="E5" t="n">
-        <v>7.052376960151654</v>
+        <v>7.078329951437117</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457193835971814</v>
+        <v>0.7457546600354336</v>
       </c>
       <c r="G5" t="n">
-        <v>32.38361181954868</v>
+        <v>32.34904085513985</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30309164547034</v>
+        <v>34.30471436162994</v>
       </c>
       <c r="I5" t="n">
-        <v>4.552369429305795</v>
+        <v>4.552072375540964</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660746147482383</v>
+        <v>4.66096662522146</v>
       </c>
       <c r="K5" t="n">
-        <v>14.17671532061473</v>
+        <v>14.18717626048733</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43940125868033</v>
+        <v>43.44094032683738</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8485221829288</v>
+        <v>99.84853208238748</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.44858440770392</v>
+        <v>84.37255366986307</v>
       </c>
       <c r="C6" t="n">
-        <v>41.56465071729342</v>
+        <v>41.48703258185139</v>
       </c>
       <c r="D6" t="n">
-        <v>2.058151630629706</v>
+        <v>2.051464041456666</v>
       </c>
       <c r="E6" t="n">
-        <v>7.462557779680821</v>
+        <v>7.476402860978706</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468377107317179</v>
+        <v>0.7468739762398986</v>
       </c>
       <c r="G6" t="n">
-        <v>31.35943652973409</v>
+        <v>31.27456031553964</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35453469365902</v>
+        <v>34.35620290703533</v>
       </c>
       <c r="I6" t="n">
-        <v>3.799330371195329</v>
+        <v>3.799087217113448</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667735692073236</v>
+        <v>4.667962351499367</v>
       </c>
       <c r="K6" t="n">
-        <v>15.55141559229608</v>
+        <v>15.62744633013694</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75747898404089</v>
+        <v>42.75907463313554</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87354529363039</v>
+        <v>99.87355354512387</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.75937206550128</v>
+        <v>82.7433553171784</v>
       </c>
       <c r="C7" t="n">
-        <v>40.46545608235083</v>
+        <v>40.4477538439071</v>
       </c>
       <c r="D7" t="n">
-        <v>1.975625924965217</v>
+        <v>1.972066379796361</v>
       </c>
       <c r="E7" t="n">
-        <v>7.691690152032518</v>
+        <v>7.715369015402011</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477913141256987</v>
+        <v>0.7478277496521483</v>
       </c>
       <c r="G7" t="n">
-        <v>30.10201720729804</v>
+        <v>30.0641433117179</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39840044978214</v>
+        <v>34.40007648399882</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170151304012048</v>
+        <v>3.169948941285235</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673695713285617</v>
+        <v>4.673923435325927</v>
       </c>
       <c r="K7" t="n">
-        <v>17.24062793449872</v>
+        <v>17.25664468282162</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18837902839503</v>
+        <v>42.1900712727959</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89446304524458</v>
+        <v>99.89446979952461</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.63277257732977</v>
+        <v>87.80172887248408</v>
       </c>
       <c r="C8" t="n">
-        <v>42.73386578641905</v>
+        <v>42.80032024115501</v>
       </c>
       <c r="D8" t="n">
-        <v>1.979872510569928</v>
+        <v>1.976370341921351</v>
       </c>
       <c r="E8" t="n">
-        <v>9.503170142807903</v>
+        <v>9.588871210164434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493986831067219</v>
+        <v>0.7494598561286309</v>
       </c>
       <c r="G8" t="n">
-        <v>30.59328041162698</v>
+        <v>30.5790289529764</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47233942290921</v>
+        <v>34.47515338191702</v>
       </c>
       <c r="I8" t="n">
-        <v>5.65096963689202</v>
+        <v>5.748721028572306</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683741769417012</v>
+        <v>4.684124100803943</v>
       </c>
       <c r="K8" t="n">
-        <v>12.36722742267023</v>
+        <v>12.19827112751591</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71094515775449</v>
+        <v>44.81020189868381</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81203836684377</v>
+        <v>99.80879326735473</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.56437843426856</v>
+        <v>85.80690034578875</v>
       </c>
       <c r="C9" t="n">
-        <v>41.5421844990631</v>
+        <v>41.69733531068609</v>
       </c>
       <c r="D9" t="n">
-        <v>1.886005598428249</v>
+        <v>1.886332624932371</v>
       </c>
       <c r="E9" t="n">
-        <v>9.838918688326181</v>
+        <v>9.95195210123425</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507760126454081</v>
+        <v>0.750857201851133</v>
       </c>
       <c r="G9" t="n">
-        <v>29.14283511820893</v>
+        <v>29.18593683037892</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53569658168878</v>
+        <v>34.53943128515211</v>
       </c>
       <c r="I9" t="n">
-        <v>4.717796355937228</v>
+        <v>4.799532790670387</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692350079033801</v>
+        <v>4.692857511569581</v>
       </c>
       <c r="K9" t="n">
-        <v>14.43562156573144</v>
+        <v>14.19309965421123</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86522255640291</v>
+        <v>43.94987833986455</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84302862119743</v>
+        <v>99.84031330476188</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.19841696846113</v>
+        <v>83.7510947920757</v>
       </c>
       <c r="C10" t="n">
-        <v>39.90782344568151</v>
+        <v>40.38587498116561</v>
       </c>
       <c r="D10" t="n">
-        <v>1.779622049030067</v>
+        <v>1.79466159256169</v>
       </c>
       <c r="E10" t="n">
-        <v>9.94021996143414</v>
+        <v>10.1359768083881</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519604623749645</v>
+        <v>0.7520543701517955</v>
       </c>
       <c r="G10" t="n">
-        <v>27.49898091014889</v>
+        <v>27.76757353401054</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59018126924837</v>
+        <v>34.59450102698259</v>
       </c>
       <c r="I10" t="n">
-        <v>3.937699426381172</v>
+        <v>4.005987646532266</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699752889843529</v>
+        <v>4.700339813448722</v>
       </c>
       <c r="K10" t="n">
-        <v>16.80158303153887</v>
+        <v>16.2489052079243</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1595436240036</v>
+        <v>43.23189945561369</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86895010122397</v>
+        <v>99.86667964470359</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.82467880350424</v>
+        <v>81.62927130427175</v>
       </c>
       <c r="C11" t="n">
-        <v>38.14394791613968</v>
+        <v>38.88482999043764</v>
       </c>
       <c r="D11" t="n">
-        <v>1.674175238287498</v>
+        <v>1.701057897994445</v>
       </c>
       <c r="E11" t="n">
-        <v>9.898882272959549</v>
+        <v>10.16446399943019</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529794741722058</v>
+        <v>0.7530809739362743</v>
       </c>
       <c r="G11" t="n">
-        <v>25.86960132518232</v>
+        <v>26.31930747498098</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63705581192147</v>
+        <v>34.64172480106861</v>
       </c>
       <c r="I11" t="n">
-        <v>3.28586296740492</v>
+        <v>3.342880069759541</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706121713576287</v>
+        <v>4.706756087101715</v>
       </c>
       <c r="K11" t="n">
-        <v>19.17532119649575</v>
+        <v>18.37072869572826</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57135034774288</v>
+        <v>42.6331638792082</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8906194603783</v>
+        <v>99.8887225653741</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.39606445573976</v>
+        <v>79.46213462492076</v>
       </c>
       <c r="C12" t="n">
-        <v>36.22339381942108</v>
+        <v>37.23506256556863</v>
       </c>
       <c r="D12" t="n">
-        <v>1.567409382418387</v>
+        <v>1.606393484091367</v>
       </c>
       <c r="E12" t="n">
-        <v>9.724510480398788</v>
+        <v>10.06364043151209</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538571653901066</v>
+        <v>0.7539620381208719</v>
       </c>
       <c r="G12" t="n">
-        <v>24.21983966146245</v>
+        <v>24.85462962986386</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67742960794491</v>
+        <v>34.6822537535601</v>
       </c>
       <c r="I12" t="n">
-        <v>2.741410874436945</v>
+        <v>2.788992549517018</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711607283688168</v>
+        <v>4.71226273825545</v>
       </c>
       <c r="K12" t="n">
-        <v>21.60393554426026</v>
+        <v>20.53786537507924</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08139666500185</v>
+        <v>42.13421427963662</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90872602868319</v>
+        <v>99.90714222028447</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.98899891459052</v>
+        <v>77.24104553826351</v>
       </c>
       <c r="C13" t="n">
-        <v>34.23930265885895</v>
+        <v>35.44489657325277</v>
       </c>
       <c r="D13" t="n">
-        <v>1.462632647924134</v>
+        <v>1.510222366042184</v>
       </c>
       <c r="E13" t="n">
-        <v>9.455588839696347</v>
+        <v>9.848902191622658</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546133806014915</v>
+        <v>0.7547190139303015</v>
       </c>
       <c r="G13" t="n">
-        <v>22.60081419296167</v>
+        <v>23.3666395801816</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71221550766862</v>
+        <v>34.71707464079386</v>
       </c>
       <c r="I13" t="n">
-        <v>2.286800716978924</v>
+        <v>2.32649390862854</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716333628759323</v>
+        <v>4.716993837064384</v>
       </c>
       <c r="K13" t="n">
-        <v>24.0110010854095</v>
+        <v>22.75895446173647</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67354595366386</v>
+        <v>41.7186769497464</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92384969793231</v>
+        <v>99.92252798473564</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.11770939813917</v>
+        <v>83.81493680021821</v>
       </c>
       <c r="C14" t="n">
-        <v>38.54895715957574</v>
+        <v>39.4931788505794</v>
       </c>
       <c r="D14" t="n">
-        <v>1.464488903496544</v>
+        <v>1.512046234623226</v>
       </c>
       <c r="E14" t="n">
-        <v>11.87167185763139</v>
+        <v>12.12262192067533</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555710751358948</v>
+        <v>0.7556304746052154</v>
       </c>
       <c r="G14" t="n">
-        <v>24.50614855543012</v>
+        <v>25.15057542748138</v>
       </c>
       <c r="H14" t="n">
-        <v>36.63292068536673</v>
+        <v>36.5147182058137</v>
       </c>
       <c r="I14" t="n">
-        <v>3.16458910147914</v>
+        <v>3.03665407073675</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722319219599344</v>
+        <v>4.722690466282597</v>
       </c>
       <c r="K14" t="n">
-        <v>16.88229060186083</v>
+        <v>16.18506319978179</v>
       </c>
       <c r="L14" t="n">
-        <v>44.46339964021468</v>
+        <v>44.22065824359042</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89464740165126</v>
+        <v>99.89890029395161</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.41733058592948</v>
+        <v>83.33748343921187</v>
       </c>
       <c r="C15" t="n">
-        <v>38.3370278435786</v>
+        <v>39.47410409209945</v>
       </c>
       <c r="D15" t="n">
-        <v>1.438919132601911</v>
+        <v>1.493649319538761</v>
       </c>
       <c r="E15" t="n">
-        <v>12.10438968935545</v>
+        <v>12.40839735997311</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756377817878404</v>
+        <v>0.7563960742166685</v>
       </c>
       <c r="G15" t="n">
-        <v>24.07827463806816</v>
+        <v>24.85565622975107</v>
       </c>
       <c r="H15" t="n">
-        <v>36.67203460048653</v>
+        <v>36.5628000020426</v>
       </c>
       <c r="I15" t="n">
-        <v>2.639973345799027</v>
+        <v>2.533108989835477</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727361361740027</v>
+        <v>4.727475463854178</v>
       </c>
       <c r="K15" t="n">
-        <v>17.58266941407051</v>
+        <v>16.66251656078814</v>
       </c>
       <c r="L15" t="n">
-        <v>43.99239748953202</v>
+        <v>43.7790278451475</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91209474718114</v>
+        <v>99.9156484980351</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.92347543264766</v>
+        <v>81.08121123035774</v>
       </c>
       <c r="C16" t="n">
-        <v>36.25076908931639</v>
+        <v>37.60964746765821</v>
       </c>
       <c r="D16" t="n">
-        <v>1.344770102074664</v>
+        <v>1.407918636278763</v>
       </c>
       <c r="E16" t="n">
-        <v>11.67939453095763</v>
+        <v>12.04832140118073</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570724584219759</v>
+        <v>0.7570530622635574</v>
       </c>
       <c r="G16" t="n">
-        <v>22.50282389689709</v>
+        <v>23.42902123345207</v>
       </c>
       <c r="H16" t="n">
-        <v>36.70571338038547</v>
+        <v>36.59455760018588</v>
       </c>
       <c r="I16" t="n">
-        <v>2.201998198773486</v>
+        <v>2.112757657849518</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73170286513735</v>
+        <v>4.731581639147233</v>
       </c>
       <c r="K16" t="n">
-        <v>20.07652456735234</v>
+        <v>18.91878876964224</v>
       </c>
       <c r="L16" t="n">
-        <v>43.5993737503924</v>
+        <v>43.40119962409301</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92666740706113</v>
+        <v>99.92963586139346</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.79357718203627</v>
+        <v>82.95789068936483</v>
       </c>
       <c r="C17" t="n">
-        <v>37.58833366839492</v>
+        <v>38.96812223972006</v>
       </c>
       <c r="D17" t="n">
-        <v>1.345991706354453</v>
+        <v>1.409111058654339</v>
       </c>
       <c r="E17" t="n">
-        <v>12.52848848502941</v>
+        <v>12.89764185288712</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577601915548672</v>
+        <v>0.7576942406581604</v>
       </c>
       <c r="G17" t="n">
-        <v>22.99023895036099</v>
+        <v>23.93667874248705</v>
       </c>
       <c r="H17" t="n">
-        <v>37.20603049833728</v>
+        <v>37.11336552640095</v>
       </c>
       <c r="I17" t="n">
-        <v>2.229066153181345</v>
+        <v>2.107810264163701</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736001197217921</v>
+        <v>4.735589004113502</v>
       </c>
       <c r="K17" t="n">
-        <v>18.20642281796372</v>
+        <v>17.04210931063517</v>
       </c>
       <c r="L17" t="n">
-        <v>44.13100874423447</v>
+        <v>43.91956756343286</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92576523059311</v>
+        <v>99.92979911378809</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.54369615073681</v>
+        <v>80.73731482703714</v>
       </c>
       <c r="C18" t="n">
-        <v>35.68219082327545</v>
+        <v>37.07330145793726</v>
       </c>
       <c r="D18" t="n">
-        <v>1.264829408695792</v>
+        <v>1.328255337373209</v>
       </c>
       <c r="E18" t="n">
-        <v>12.08286366059576</v>
+        <v>12.45053054409727</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583505077132926</v>
+        <v>0.7582441153875631</v>
       </c>
       <c r="G18" t="n">
-        <v>21.60394466034138</v>
+        <v>22.56317633974049</v>
       </c>
       <c r="H18" t="n">
-        <v>37.23501502568355</v>
+        <v>37.14029948040373</v>
       </c>
       <c r="I18" t="n">
-        <v>1.859002214498964</v>
+        <v>1.757783288862611</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73969067320808</v>
+        <v>4.739025721172269</v>
       </c>
       <c r="K18" t="n">
-        <v>20.45630384926318</v>
+        <v>19.26268517296286</v>
       </c>
       <c r="L18" t="n">
-        <v>43.79958682320633</v>
+        <v>43.6054630839842</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93808149574495</v>
+        <v>99.94144971488433</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.70684459015979</v>
+        <v>79.8591316881113</v>
       </c>
       <c r="C19" t="n">
-        <v>35.13133142878294</v>
+        <v>36.4661597655703</v>
       </c>
       <c r="D19" t="n">
-        <v>1.235355942829267</v>
+        <v>1.29695177164969</v>
       </c>
       <c r="E19" t="n">
-        <v>12.05966910825581</v>
+        <v>12.40138945602874</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588483822523926</v>
+        <v>0.758708003145942</v>
       </c>
       <c r="G19" t="n">
-        <v>21.10052252202674</v>
+        <v>22.03142024314596</v>
       </c>
       <c r="H19" t="n">
-        <v>37.25946066889964</v>
+        <v>37.16302162215445</v>
       </c>
       <c r="I19" t="n">
-        <v>1.550185576818495</v>
+        <v>1.465715572324388</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742802389077455</v>
+        <v>4.741925019662138</v>
       </c>
       <c r="K19" t="n">
-        <v>21.2931554098402</v>
+        <v>20.14086831188867</v>
       </c>
       <c r="L19" t="n">
-        <v>43.5238742109741</v>
+        <v>43.34414460896151</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94836104959724</v>
+        <v>99.95117268642048</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.29172560275856</v>
+        <v>77.41899776920587</v>
       </c>
       <c r="C20" t="n">
-        <v>32.95458052029888</v>
+        <v>34.25190716233217</v>
       </c>
       <c r="D20" t="n">
-        <v>1.149262815112768</v>
+        <v>1.209013359461885</v>
       </c>
       <c r="E20" t="n">
-        <v>11.43464446930208</v>
+        <v>11.76420537744532</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592769346804622</v>
+        <v>0.7591072143994491</v>
       </c>
       <c r="G20" t="n">
-        <v>19.6300070880594</v>
+        <v>20.53760362114454</v>
       </c>
       <c r="H20" t="n">
-        <v>37.2805025959982</v>
+        <v>37.1825757805189</v>
       </c>
       <c r="I20" t="n">
-        <v>1.29255085785276</v>
+        <v>1.222072326239232</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74548084175289</v>
+        <v>4.744420089996557</v>
       </c>
       <c r="K20" t="n">
-        <v>23.70827439724144</v>
+        <v>22.58100223079412</v>
       </c>
       <c r="L20" t="n">
-        <v>43.2940843719925</v>
+        <v>43.12637628542025</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95693928953281</v>
+        <v>99.95928567854654</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.22324888227693</v>
+        <v>82.98829541576535</v>
       </c>
       <c r="C21" t="n">
-        <v>36.56029418205877</v>
+        <v>37.66798399472124</v>
       </c>
       <c r="D21" t="n">
-        <v>1.150167601151538</v>
+        <v>1.209880057744565</v>
       </c>
       <c r="E21" t="n">
-        <v>13.40044093504431</v>
+        <v>13.62161222257168</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598746945322777</v>
+        <v>0.7596513911150665</v>
       </c>
       <c r="G21" t="n">
-        <v>21.27859396189555</v>
+        <v>22.10384314901118</v>
       </c>
       <c r="H21" t="n">
-        <v>38.94298526608126</v>
+        <v>38.76074749149409</v>
       </c>
       <c r="I21" t="n">
-        <v>1.941969582745277</v>
+        <v>1.784739909359585</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749216840826738</v>
+        <v>4.747821194469165</v>
       </c>
       <c r="K21" t="n">
-        <v>17.77675111772306</v>
+        <v>17.01170458423465</v>
       </c>
       <c r="L21" t="n">
-        <v>45.59827330284922</v>
+        <v>45.26086270738119</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93531860263104</v>
+        <v>99.94055128633707</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_82_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.35043813460899</v>
+        <v>44.61847635228653</v>
       </c>
       <c r="M2" t="n">
-        <v>100.5884629968408</v>
+        <v>93.25680546140683</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00211194501367</v>
+        <v>81.45318130424533</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93593280295305</v>
+        <v>43.20873685980089</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228660463097383</v>
+        <v>2.178697251042954</v>
       </c>
       <c r="E3" t="n">
-        <v>5.709032593426138</v>
+        <v>4.151780849473969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742886821032461</v>
+        <v>0.7376162331371376</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97591898637718</v>
+        <v>32.7712378177711</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1727937674932</v>
+        <v>33.93034672430833</v>
       </c>
       <c r="I3" t="n">
-        <v>6.529776682134408</v>
+        <v>3.07340097140474</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643042631452881</v>
+        <v>4.610101457107111</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99788805498635</v>
+        <v>18.54681869575467</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83178626651026</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7656071244497</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.03019665194029</v>
+        <v>88.55316816826125</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59149699893401</v>
+        <v>42.7954601876528</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181527688555789</v>
+        <v>2.184440355727511</v>
       </c>
       <c r="E4" t="n">
-        <v>6.49710275461477</v>
+        <v>6.527719599334371</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444383310710321</v>
+        <v>0.7395606094114949</v>
       </c>
       <c r="G4" t="n">
-        <v>33.25738004518612</v>
+        <v>33.45654960986474</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24416322926747</v>
+        <v>34.01978803292877</v>
       </c>
       <c r="I4" t="n">
-        <v>5.452845034051149</v>
+        <v>7.00285615217253</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65273956919395</v>
+        <v>4.622253808821844</v>
       </c>
       <c r="K4" t="n">
-        <v>12.96980334805973</v>
+        <v>11.44683183173873</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25731696739142</v>
+        <v>45.52489314837645</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81861731438515</v>
+        <v>99.76718516776799</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.81282373951268</v>
+        <v>87.49937336164231</v>
       </c>
       <c r="C5" t="n">
-        <v>42.22041549506277</v>
+        <v>42.8270942777431</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12194491050791</v>
+        <v>2.134596773595071</v>
       </c>
       <c r="E5" t="n">
-        <v>7.078329951437117</v>
+        <v>7.353559016278512</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457546600354336</v>
+        <v>0.7412084231063492</v>
       </c>
       <c r="G5" t="n">
-        <v>32.34904085513985</v>
+        <v>32.69315303830125</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30471436162994</v>
+        <v>34.09558746289206</v>
       </c>
       <c r="I5" t="n">
-        <v>4.552072375540964</v>
+        <v>5.848716003054385</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66096662522146</v>
+        <v>4.632552644414683</v>
       </c>
       <c r="K5" t="n">
-        <v>14.18717626048733</v>
+        <v>12.5006266383577</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44094032683738</v>
+        <v>44.47775530189438</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84853208238748</v>
+        <v>99.80547621799518</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.37255366986307</v>
+        <v>86.22325048727699</v>
       </c>
       <c r="C6" t="n">
-        <v>41.48703258185139</v>
+        <v>42.45871604400675</v>
       </c>
       <c r="D6" t="n">
-        <v>2.051464041456666</v>
+        <v>2.073925974468346</v>
       </c>
       <c r="E6" t="n">
-        <v>7.476402860978706</v>
+        <v>7.958406875658349</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468739762398986</v>
+        <v>0.742607665871441</v>
       </c>
       <c r="G6" t="n">
-        <v>31.27456031553964</v>
+        <v>31.7639284909103</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35620290703533</v>
+        <v>34.15995263008628</v>
       </c>
       <c r="I6" t="n">
-        <v>3.799087217113448</v>
+        <v>4.883130938585746</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667962351499367</v>
+        <v>4.641297911696507</v>
       </c>
       <c r="K6" t="n">
-        <v>15.62744633013694</v>
+        <v>13.77674951272303</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75907463313554</v>
+        <v>43.60207010985206</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87355354512387</v>
+        <v>99.83753566658183</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.7433553171784</v>
+        <v>84.76186472778542</v>
       </c>
       <c r="C7" t="n">
-        <v>40.4477538439071</v>
+        <v>41.75569587777601</v>
       </c>
       <c r="D7" t="n">
-        <v>1.972066379796361</v>
+        <v>2.004620119859417</v>
       </c>
       <c r="E7" t="n">
-        <v>7.715369015402011</v>
+        <v>8.37175484949389</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478277496521483</v>
+        <v>0.7437979491791257</v>
       </c>
       <c r="G7" t="n">
-        <v>30.0641433117179</v>
+        <v>30.70245077333468</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40007648399882</v>
+        <v>34.21470566223978</v>
       </c>
       <c r="I7" t="n">
-        <v>3.169948941285235</v>
+        <v>4.075798191308996</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673923435325927</v>
+        <v>4.648737182369536</v>
       </c>
       <c r="K7" t="n">
-        <v>17.25664468282162</v>
+        <v>15.23813527221459</v>
       </c>
       <c r="L7" t="n">
-        <v>42.1900712727959</v>
+        <v>42.87052632393758</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89446979952461</v>
+        <v>99.86435747392817</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.80172887248408</v>
+        <v>83.08296289542308</v>
       </c>
       <c r="C8" t="n">
-        <v>42.80032024115501</v>
+        <v>40.70980494163104</v>
       </c>
       <c r="D8" t="n">
-        <v>1.976370341921351</v>
+        <v>1.925314410123513</v>
       </c>
       <c r="E8" t="n">
-        <v>9.588871210164434</v>
+        <v>8.607411491238908</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494598561286309</v>
+        <v>0.7448129009041425</v>
       </c>
       <c r="G8" t="n">
-        <v>30.5790289529764</v>
+        <v>29.48781682594033</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47515338191702</v>
+        <v>34.26139344159056</v>
       </c>
       <c r="I8" t="n">
-        <v>5.748721028572306</v>
+        <v>3.40113319497474</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684124100803943</v>
+        <v>4.655080630650891</v>
       </c>
       <c r="K8" t="n">
-        <v>12.19827112751591</v>
+        <v>16.91703710457691</v>
       </c>
       <c r="L8" t="n">
-        <v>44.81020189868381</v>
+        <v>42.25994133736681</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80879326735473</v>
+        <v>99.88678338357477</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.80690034578875</v>
+        <v>81.17243978896573</v>
       </c>
       <c r="C9" t="n">
-        <v>41.69733531068609</v>
+        <v>39.32721213216269</v>
       </c>
       <c r="D9" t="n">
-        <v>1.886332624932371</v>
+        <v>1.835539039873221</v>
       </c>
       <c r="E9" t="n">
-        <v>9.95195210123425</v>
+        <v>8.678987066367707</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750857201851133</v>
+        <v>0.7456807925264272</v>
       </c>
       <c r="G9" t="n">
-        <v>29.18593683037892</v>
+        <v>28.1128311822959</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53943128515211</v>
+        <v>34.30131645621565</v>
       </c>
       <c r="I9" t="n">
-        <v>4.799532790670387</v>
+        <v>2.837580298396652</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692857511569581</v>
+        <v>4.660504953290171</v>
       </c>
       <c r="K9" t="n">
-        <v>14.19309965421123</v>
+        <v>18.82756021103426</v>
       </c>
       <c r="L9" t="n">
-        <v>43.94987833986455</v>
+        <v>41.7507517347204</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84031330476188</v>
+        <v>99.90552407791736</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.7510947920757</v>
+        <v>85.93213462928873</v>
       </c>
       <c r="C10" t="n">
-        <v>40.38587498116561</v>
+        <v>42.63297341890394</v>
       </c>
       <c r="D10" t="n">
-        <v>1.79466159256169</v>
+        <v>1.837570421338846</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1359768083881</v>
+        <v>10.55811521273538</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520543701517955</v>
+        <v>0.7465060335636949</v>
       </c>
       <c r="G10" t="n">
-        <v>27.76757353401054</v>
+        <v>29.53796344021208</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59450102698259</v>
+        <v>35.73329747845263</v>
       </c>
       <c r="I10" t="n">
-        <v>4.005987646532266</v>
+        <v>2.853019333212982</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700339813448722</v>
+        <v>4.665662709773095</v>
       </c>
       <c r="K10" t="n">
-        <v>16.2489052079243</v>
+        <v>14.06786537071129</v>
       </c>
       <c r="L10" t="n">
-        <v>43.23189945561369</v>
+        <v>43.20416569698271</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86667964470359</v>
+        <v>99.90500448659795</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.62927130427175</v>
+        <v>85.5806787686454</v>
       </c>
       <c r="C11" t="n">
-        <v>38.88482999043764</v>
+        <v>42.59557340200177</v>
       </c>
       <c r="D11" t="n">
-        <v>1.701057897994445</v>
+        <v>1.812619338876305</v>
       </c>
       <c r="E11" t="n">
-        <v>10.16446399943019</v>
+        <v>10.88117096909503</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530809739362743</v>
+        <v>0.7472180163199548</v>
       </c>
       <c r="G11" t="n">
-        <v>26.31930747498098</v>
+        <v>29.19519075572468</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64172480106861</v>
+        <v>35.82568088131954</v>
       </c>
       <c r="I11" t="n">
-        <v>3.342880069759541</v>
+        <v>2.448686205310164</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706756087101715</v>
+        <v>4.670112601999718</v>
       </c>
       <c r="K11" t="n">
-        <v>18.37072869572826</v>
+        <v>14.4193212313546</v>
       </c>
       <c r="L11" t="n">
-        <v>42.6331638792082</v>
+        <v>42.90356026705895</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8887225653741</v>
+        <v>99.91845490041531</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.46213462492076</v>
+        <v>83.62244552784654</v>
       </c>
       <c r="C12" t="n">
-        <v>37.23506256556863</v>
+        <v>41.0180611455102</v>
       </c>
       <c r="D12" t="n">
-        <v>1.606393484091367</v>
+        <v>1.729289316047711</v>
       </c>
       <c r="E12" t="n">
-        <v>10.06364043151209</v>
+        <v>10.72131222426063</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539620381208719</v>
+        <v>0.7478263032794246</v>
       </c>
       <c r="G12" t="n">
-        <v>24.85462962986386</v>
+        <v>27.85302483043566</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6822537535601</v>
+        <v>35.85484545446723</v>
       </c>
       <c r="I12" t="n">
-        <v>2.788992549517018</v>
+        <v>2.042233003859474</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71226273825545</v>
+        <v>4.673914395496404</v>
       </c>
       <c r="K12" t="n">
-        <v>20.53786537507924</v>
+        <v>16.37755447215346</v>
       </c>
       <c r="L12" t="n">
-        <v>42.13421427963662</v>
+        <v>42.53636532107773</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90714222028447</v>
+        <v>99.93198093874139</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.24104553826351</v>
+        <v>84.73618921092934</v>
       </c>
       <c r="C13" t="n">
-        <v>35.44489657325277</v>
+        <v>41.96863130300924</v>
       </c>
       <c r="D13" t="n">
-        <v>1.510222366042184</v>
+        <v>1.730565005775162</v>
       </c>
       <c r="E13" t="n">
-        <v>9.848902191622658</v>
+        <v>11.3444227661769</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547190139303015</v>
+        <v>0.7483779717157922</v>
       </c>
       <c r="G13" t="n">
-        <v>23.3666395801816</v>
+        <v>28.17622564874435</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71707464079386</v>
+        <v>36.18394918345504</v>
       </c>
       <c r="I13" t="n">
-        <v>2.32649390862854</v>
+        <v>1.875286311838378</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716993837064384</v>
+        <v>4.677362323223702</v>
       </c>
       <c r="K13" t="n">
-        <v>22.75895446173647</v>
+        <v>15.26381078907067</v>
       </c>
       <c r="L13" t="n">
-        <v>41.7186769497464</v>
+        <v>42.70509444323717</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92252798473564</v>
+        <v>99.93753653531707</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.81493680021821</v>
+        <v>82.68919616018951</v>
       </c>
       <c r="C14" t="n">
-        <v>39.4931788505794</v>
+        <v>40.21305477387217</v>
       </c>
       <c r="D14" t="n">
-        <v>1.512046234623226</v>
+        <v>1.645726595962489</v>
       </c>
       <c r="E14" t="n">
-        <v>12.12262192067533</v>
+        <v>11.04889970197237</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556304746052154</v>
+        <v>0.7488497207121971</v>
       </c>
       <c r="G14" t="n">
-        <v>25.15057542748138</v>
+        <v>26.79492753478427</v>
       </c>
       <c r="H14" t="n">
-        <v>36.5147182058137</v>
+        <v>36.20675816816383</v>
       </c>
       <c r="I14" t="n">
-        <v>3.03665407073675</v>
+        <v>1.563723684143127</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722690466282597</v>
+        <v>4.680310754451233</v>
       </c>
       <c r="K14" t="n">
-        <v>16.18506319978179</v>
+        <v>17.31080383981048</v>
       </c>
       <c r="L14" t="n">
-        <v>44.22065824359042</v>
+        <v>42.42405009987739</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89890029395161</v>
+        <v>99.94790871356004</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.33748343921187</v>
+        <v>81.75122458607505</v>
       </c>
       <c r="C15" t="n">
-        <v>39.47410409209945</v>
+        <v>39.49544959742104</v>
       </c>
       <c r="D15" t="n">
-        <v>1.493649319538761</v>
+        <v>1.606431464185988</v>
       </c>
       <c r="E15" t="n">
-        <v>12.40839735997311</v>
+        <v>11.00596266643423</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563960742166685</v>
+        <v>0.7492543744147662</v>
       </c>
       <c r="G15" t="n">
-        <v>24.85565622975107</v>
+        <v>26.15514313134553</v>
       </c>
       <c r="H15" t="n">
-        <v>36.5628000020426</v>
+        <v>36.22632310668959</v>
       </c>
       <c r="I15" t="n">
-        <v>2.533108989835477</v>
+        <v>1.325270002912674</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727475463854178</v>
+        <v>4.682839840092289</v>
       </c>
       <c r="K15" t="n">
-        <v>16.66251656078814</v>
+        <v>18.24877541392492</v>
       </c>
       <c r="L15" t="n">
-        <v>43.7790278451475</v>
+        <v>42.21162318007213</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9156484980351</v>
+        <v>99.95584819141811</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.08121123035774</v>
+        <v>79.27868317545243</v>
       </c>
       <c r="C16" t="n">
-        <v>37.60964746765821</v>
+        <v>37.22831550394019</v>
       </c>
       <c r="D16" t="n">
-        <v>1.407918636278763</v>
+        <v>1.504674120367688</v>
       </c>
       <c r="E16" t="n">
-        <v>12.04832140118073</v>
+        <v>10.4929548447421</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570530622635574</v>
+        <v>0.7496024523050215</v>
       </c>
       <c r="G16" t="n">
-        <v>23.42902123345207</v>
+        <v>24.49837908534137</v>
       </c>
       <c r="H16" t="n">
-        <v>36.59455760018588</v>
+        <v>36.24315261419635</v>
       </c>
       <c r="I16" t="n">
-        <v>2.112757657849518</v>
+        <v>1.104904731593522</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731581639147233</v>
+        <v>4.685015326906385</v>
       </c>
       <c r="K16" t="n">
-        <v>18.91878876964224</v>
+        <v>20.72131682454756</v>
       </c>
       <c r="L16" t="n">
-        <v>43.40119962409301</v>
+        <v>42.01355461587578</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92963586139346</v>
+        <v>99.96318694436353</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.95789068936483</v>
+        <v>84.15749802666105</v>
       </c>
       <c r="C17" t="n">
-        <v>38.96812223972006</v>
+        <v>40.46982168687588</v>
       </c>
       <c r="D17" t="n">
-        <v>1.409111058654339</v>
+        <v>1.505394279535378</v>
       </c>
       <c r="E17" t="n">
-        <v>12.89764185288712</v>
+        <v>12.21155163806238</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576942406581604</v>
+        <v>0.7499612230653099</v>
       </c>
       <c r="G17" t="n">
-        <v>23.93667874248705</v>
+        <v>26.02228399818123</v>
       </c>
       <c r="H17" t="n">
-        <v>37.11336552640095</v>
+        <v>37.77267874841217</v>
       </c>
       <c r="I17" t="n">
-        <v>2.107810264163701</v>
+        <v>1.208370495246382</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735589004113502</v>
+        <v>4.687257644158187</v>
       </c>
       <c r="K17" t="n">
-        <v>17.04210931063517</v>
+        <v>15.84250197333895</v>
       </c>
       <c r="L17" t="n">
-        <v>43.91956756343286</v>
+        <v>43.64741659218438</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92979911378809</v>
+        <v>99.95974025239921</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.73731482703714</v>
+        <v>85.794189259365</v>
       </c>
       <c r="C18" t="n">
-        <v>37.07330145793726</v>
+        <v>41.19734144943531</v>
       </c>
       <c r="D18" t="n">
-        <v>1.328255337373209</v>
+        <v>1.50660478371444</v>
       </c>
       <c r="E18" t="n">
-        <v>12.45053054409727</v>
+        <v>12.80883100285079</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582441153875631</v>
+        <v>0.7505642751739808</v>
       </c>
       <c r="G18" t="n">
-        <v>22.56317633974049</v>
+        <v>26.16446862530336</v>
       </c>
       <c r="H18" t="n">
-        <v>37.14029948040373</v>
+        <v>37.80305217688928</v>
       </c>
       <c r="I18" t="n">
-        <v>1.757783288862611</v>
+        <v>2.069641675595771</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739025721172269</v>
+        <v>4.691026719837381</v>
       </c>
       <c r="K18" t="n">
-        <v>19.26268517296286</v>
+        <v>14.20581074063501</v>
       </c>
       <c r="L18" t="n">
-        <v>43.6054630839842</v>
+        <v>44.52791518356324</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94144971488433</v>
+        <v>99.93106737363355</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.8591316881113</v>
+        <v>83.00608468416631</v>
       </c>
       <c r="C19" t="n">
-        <v>36.4661597655703</v>
+        <v>38.72981434456552</v>
       </c>
       <c r="D19" t="n">
-        <v>1.29695177164969</v>
+        <v>1.403807752972609</v>
       </c>
       <c r="E19" t="n">
-        <v>12.40138945602874</v>
+        <v>12.22252213593296</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758708003145942</v>
+        <v>0.7510844765746527</v>
       </c>
       <c r="G19" t="n">
-        <v>22.03142024314596</v>
+        <v>24.37924285495377</v>
       </c>
       <c r="H19" t="n">
-        <v>37.16302162215445</v>
+        <v>37.82925273204831</v>
       </c>
       <c r="I19" t="n">
-        <v>1.465715572324388</v>
+        <v>1.725896753092431</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741925019662138</v>
+        <v>4.69427797859158</v>
       </c>
       <c r="K19" t="n">
-        <v>20.14086831188867</v>
+        <v>16.99391531583369</v>
       </c>
       <c r="L19" t="n">
-        <v>43.34414460896151</v>
+        <v>44.21878029305647</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95117268642048</v>
+        <v>99.94250995345568</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.41899776920587</v>
+        <v>80.13280367814717</v>
       </c>
       <c r="C20" t="n">
-        <v>34.25190716233217</v>
+        <v>36.1230840967888</v>
       </c>
       <c r="D20" t="n">
-        <v>1.209013359461885</v>
+        <v>1.298454516346804</v>
       </c>
       <c r="E20" t="n">
-        <v>11.76420537744532</v>
+        <v>11.54509530296781</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591072143994491</v>
+        <v>0.7515341017962959</v>
       </c>
       <c r="G20" t="n">
-        <v>20.53760362114454</v>
+        <v>22.54962470687247</v>
       </c>
       <c r="H20" t="n">
-        <v>37.1825757805189</v>
+        <v>37.85189863497232</v>
       </c>
       <c r="I20" t="n">
-        <v>1.222072326239232</v>
+        <v>1.439108278964614</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744420089996557</v>
+        <v>4.697088136226849</v>
       </c>
       <c r="K20" t="n">
-        <v>22.58100223079412</v>
+        <v>19.86719632185283</v>
       </c>
       <c r="L20" t="n">
-        <v>43.12637628542025</v>
+        <v>43.96177800488358</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95928567854654</v>
+        <v>99.95205842352522</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.98829541576535</v>
+        <v>77.30764794459022</v>
       </c>
       <c r="C21" t="n">
-        <v>37.66798399472124</v>
+        <v>33.51942904428261</v>
       </c>
       <c r="D21" t="n">
-        <v>1.209880057744565</v>
+        <v>1.195427362412366</v>
       </c>
       <c r="E21" t="n">
-        <v>13.62161222257168</v>
+        <v>10.82901789001797</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596513911150665</v>
+        <v>0.7519229157400198</v>
       </c>
       <c r="G21" t="n">
-        <v>22.10384314901118</v>
+        <v>20.76040249955547</v>
       </c>
       <c r="H21" t="n">
-        <v>38.76074749149409</v>
+        <v>37.87148170638655</v>
       </c>
       <c r="I21" t="n">
-        <v>1.784739909359585</v>
+        <v>1.199877347102716</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747821194469165</v>
+        <v>4.699518223375124</v>
       </c>
       <c r="K21" t="n">
-        <v>17.01170458423465</v>
+        <v>22.6923520554098</v>
       </c>
       <c r="L21" t="n">
-        <v>45.26086270738119</v>
+        <v>43.74824367033635</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94055128633707</v>
+        <v>99.96002477002875</v>
       </c>
     </row>
   </sheetData>
